--- a/exemples/CEM-20-divisions.xlsx
+++ b/exemples/CEM-20-divisions.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Salles" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Enseignants" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Classes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Programme" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Reglages" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Programme" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -818,106 +819,134 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Programme annuel</t>
+          <t>Réglages</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Qui enseigne quoi, à qui, combien d'heures. Pour un fouj (dédoublement), deux lignes partagent le même identifiant de couplage, l'une en G1 et l'autre en G2.</t>
+          <t>Le type de salle que suivent les cours sans exigence particulière. Il DOIT correspondre au type des salles ordinaires de la feuille Salles, sans quoi aucune génération ne peut aboutir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Classe</t>
+          <t xml:space="preserve">   Type de salle ordinaire</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>(obligatoire) Nom d'une division.</t>
+          <t>(obligatoire) Exemple : classroom, ou classique. Doit exister dans Salles.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Matière</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>(obligatoire) Nom d'une matière.</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Enseignant</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Programme annuel</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>(obligatoire) Nom, ou « Prénom Nom » si plusieurs homonymes.</t>
+          <t>Qui enseigne quoi, à qui, combien d'heures. Pour un fouj (dédoublement), deux lignes partagent le même identifiant de couplage, l'une en G1 et l'autre en G2.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Heures par semaine</t>
+          <t xml:space="preserve">   Classe</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>(obligatoire) Volume hebdomadaire.</t>
+          <t>(obligatoire) Nom d'une division.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Blocs de 2 h</t>
+          <t xml:space="preserve">   Matière</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>(facultatif) Nombre de séances doubles à réserver dans ce volume.</t>
+          <t>(obligatoire) Nom d'une matière.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Max par jour</t>
+          <t xml:space="preserve">   Enseignant</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>(facultatif) Plafond de cette matière dans une journée.</t>
+          <t>(obligatoire) Nom, ou « Prénom Nom » si plusieurs homonymes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fouj (couplage)</t>
+          <t xml:space="preserve">   Heures par semaine</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>(facultatif) Même libellé sur les deux lignes d'un dédoublement.</t>
+          <t>(obligatoire) Volume hebdomadaire.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Blocs de 2 h</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>(facultatif) Nombre de séances doubles à réserver dans ce volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Max par jour</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>(facultatif) Plafond de cette matière dans une journée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fouj (couplage)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>(facultatif) Même libellé sur les deux lignes d'un dédoublement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Groupe</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>(facultatif) G1 ou G2, pour un fouj.</t>
         </is>
@@ -3527,6 +3556,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Type de salle ordinaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
